--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/82.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/82.xlsx
@@ -426,13 +426,13 @@
         <v>-10.04343790658347</v>
       </c>
       <c r="E2">
-        <v>-13.73341010181533</v>
+        <v>-13.0167790901015</v>
       </c>
       <c r="F2">
-        <v>0.122329837328312</v>
+        <v>-0.1387052986418682</v>
       </c>
       <c r="G2">
-        <v>-14.45588227117853</v>
+        <v>-12.00685323977404</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.620319569011615</v>
       </c>
       <c r="E3">
-        <v>-14.4100909158335</v>
+        <v>-14.13983611552974</v>
       </c>
       <c r="F3">
-        <v>0.1394463929723582</v>
+        <v>-0.3504964776178262</v>
       </c>
       <c r="G3">
-        <v>-13.96583545718237</v>
+        <v>-12.68735242809893</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.111633576768771</v>
       </c>
       <c r="E4">
-        <v>-14.74127180543646</v>
+        <v>-15.10351802673203</v>
       </c>
       <c r="F4">
-        <v>0.3699860113758774</v>
+        <v>0.09861616368837059</v>
       </c>
       <c r="G4">
-        <v>-13.87350268681933</v>
+        <v>-11.9435158825167</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.552124894559455</v>
       </c>
       <c r="E5">
-        <v>-14.91958952643649</v>
+        <v>-15.14378521760824</v>
       </c>
       <c r="F5">
-        <v>0.7311326614439891</v>
+        <v>-0.1691925325345012</v>
       </c>
       <c r="G5">
-        <v>-13.2313015445655</v>
+        <v>-12.49088810307088</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.939990857009688</v>
       </c>
       <c r="E6">
-        <v>-15.7944861762444</v>
+        <v>-16.10752147049862</v>
       </c>
       <c r="F6">
-        <v>0.8162871737169727</v>
+        <v>0.1034687399339701</v>
       </c>
       <c r="G6">
-        <v>-12.66885309962548</v>
+        <v>-11.49779065220031</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.292646375621322</v>
       </c>
       <c r="E7">
-        <v>-16.87815906322793</v>
+        <v>-16.35565920374892</v>
       </c>
       <c r="F7">
-        <v>0.8658980974706351</v>
+        <v>0.1255430744837713</v>
       </c>
       <c r="G7">
-        <v>-12.37534675320478</v>
+        <v>-11.45886194720402</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.609384394888433</v>
       </c>
       <c r="E8">
-        <v>-16.65835599184362</v>
+        <v>-17.11961729731691</v>
       </c>
       <c r="F8">
-        <v>1.01692272887943</v>
+        <v>0.4829736683829244</v>
       </c>
       <c r="G8">
-        <v>-11.8502379514022</v>
+        <v>-11.34449253045882</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.912985618626585</v>
       </c>
       <c r="E9">
-        <v>-17.76706228314156</v>
+        <v>-17.99453206102085</v>
       </c>
       <c r="F9">
-        <v>1.012245766523224</v>
+        <v>0.6482909509596217</v>
       </c>
       <c r="G9">
-        <v>-12.01280891119919</v>
+        <v>-10.9243081589779</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.208136456159745</v>
       </c>
       <c r="E10">
-        <v>-18.28799529061392</v>
+        <v>-18.53935276888367</v>
       </c>
       <c r="F10">
-        <v>1.137577754566789</v>
+        <v>0.5138402945460396</v>
       </c>
       <c r="G10">
-        <v>-11.58065029650273</v>
+        <v>-10.37165230774305</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.512189606561406</v>
       </c>
       <c r="E11">
-        <v>-19.35632570765946</v>
+        <v>-19.13851063636453</v>
       </c>
       <c r="F11">
-        <v>1.49209912214731</v>
+        <v>0.7512702730060451</v>
       </c>
       <c r="G11">
-        <v>-10.13330627109768</v>
+        <v>-9.873560868086461</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.841487258600521</v>
       </c>
       <c r="E12">
-        <v>-19.42633591581805</v>
+        <v>-19.21791289961502</v>
       </c>
       <c r="F12">
-        <v>1.789700052011866</v>
+        <v>1.072188088524602</v>
       </c>
       <c r="G12">
-        <v>-9.820476270364248</v>
+        <v>-9.065744719412281</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.205173131573852</v>
       </c>
       <c r="E13">
-        <v>-19.78074334860634</v>
+        <v>-20.23401189745609</v>
       </c>
       <c r="F13">
-        <v>1.800200437209753</v>
+        <v>1.262551887892345</v>
       </c>
       <c r="G13">
-        <v>-9.340457098806542</v>
+        <v>-8.924424151431872</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.629891606273316</v>
       </c>
       <c r="E14">
-        <v>-20.30329754977345</v>
+        <v>-21.05598880001036</v>
       </c>
       <c r="F14">
-        <v>1.618599108228823</v>
+        <v>1.240371522314985</v>
       </c>
       <c r="G14">
-        <v>-8.889146978165398</v>
+        <v>-8.353891354284954</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.127643505131651</v>
       </c>
       <c r="E15">
-        <v>-21.58466549803584</v>
+        <v>-21.60297864692286</v>
       </c>
       <c r="F15">
-        <v>2.061517218096885</v>
+        <v>1.578042240187759</v>
       </c>
       <c r="G15">
-        <v>-8.477248902169277</v>
+        <v>-8.073421936197899</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.713395154825109</v>
       </c>
       <c r="E16">
-        <v>-21.65744260381311</v>
+        <v>-21.71071557203934</v>
       </c>
       <c r="F16">
-        <v>1.990514534533328</v>
+        <v>1.531464797863148</v>
       </c>
       <c r="G16">
-        <v>-7.990284206070182</v>
+        <v>-6.911807785741807</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.392875873286963</v>
       </c>
       <c r="E17">
-        <v>-23.53134326208313</v>
+        <v>-23.38713400730887</v>
       </c>
       <c r="F17">
-        <v>2.272745935606342</v>
+        <v>1.828671424843972</v>
       </c>
       <c r="G17">
-        <v>-7.751388618865295</v>
+        <v>-6.721064083405619</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.153570432015973</v>
       </c>
       <c r="E18">
-        <v>-22.89478019929892</v>
+        <v>-23.22124241898588</v>
       </c>
       <c r="F18">
-        <v>2.085100838054587</v>
+        <v>2.612699634041231</v>
       </c>
       <c r="G18">
-        <v>-7.430633172110849</v>
+        <v>-5.949210390924542</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.9843325814147533</v>
       </c>
       <c r="E19">
-        <v>-24.40985816262317</v>
+        <v>-24.88867636182419</v>
       </c>
       <c r="F19">
-        <v>2.640970156763972</v>
+        <v>2.310603982649085</v>
       </c>
       <c r="G19">
-        <v>-6.880172212568532</v>
+        <v>-6.004516364703607</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.857698971671738</v>
       </c>
       <c r="E20">
-        <v>-24.56392590531213</v>
+        <v>-24.94280521163788</v>
       </c>
       <c r="F20">
-        <v>3.090934359760247</v>
+        <v>2.591877791004463</v>
       </c>
       <c r="G20">
-        <v>-6.13431954475289</v>
+        <v>-5.885439352201561</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.7488286185402959</v>
       </c>
       <c r="E21">
-        <v>-24.72137641808482</v>
+        <v>-25.27697036561189</v>
       </c>
       <c r="F21">
-        <v>2.661382786303758</v>
+        <v>2.808472672549255</v>
       </c>
       <c r="G21">
-        <v>-6.034857514571027</v>
+        <v>-5.550292963987904</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.6347337946013554</v>
       </c>
       <c r="E22">
-        <v>-25.37195963639678</v>
+        <v>-26.2389540990613</v>
       </c>
       <c r="F22">
-        <v>2.944742423779385</v>
+        <v>2.831670273297252</v>
       </c>
       <c r="G22">
-        <v>-5.419926991196943</v>
+        <v>-5.311082874956785</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.4957192070755478</v>
       </c>
       <c r="E23">
-        <v>-25.79182616096595</v>
+        <v>-26.66272869669909</v>
       </c>
       <c r="F23">
-        <v>2.948524749340567</v>
+        <v>2.647761112732123</v>
       </c>
       <c r="G23">
-        <v>-5.778111465818389</v>
+        <v>-4.436704897670018</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.3274688778377254</v>
       </c>
       <c r="E24">
-        <v>-26.40752201552282</v>
+        <v>-26.53016667707256</v>
       </c>
       <c r="F24">
-        <v>3.391586995136716</v>
+        <v>3.217843559338743</v>
       </c>
       <c r="G24">
-        <v>-6.03661541425238</v>
+        <v>-3.984855158105973</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.1315673967404014</v>
       </c>
       <c r="E25">
-        <v>-26.06463049213603</v>
+        <v>-27.5061569806277</v>
       </c>
       <c r="F25">
-        <v>3.082562878787555</v>
+        <v>3.077642376414926</v>
       </c>
       <c r="G25">
-        <v>-5.470485642672693</v>
+        <v>-4.556023579996431</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.08039836703019065</v>
       </c>
       <c r="E26">
-        <v>-26.71256455315351</v>
+        <v>-27.00876298104721</v>
       </c>
       <c r="F26">
-        <v>3.475041697499155</v>
+        <v>3.205825605058927</v>
       </c>
       <c r="G26">
-        <v>-5.658905342040312</v>
+        <v>-5.047457512573542</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.2898838308243488</v>
       </c>
       <c r="E27">
-        <v>-26.77408387254771</v>
+        <v>-26.76278532989857</v>
       </c>
       <c r="F27">
-        <v>3.454764920213429</v>
+        <v>2.966117616241223</v>
       </c>
       <c r="G27">
-        <v>-5.78328584849627</v>
+        <v>-4.045729469482091</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.4779838782691074</v>
       </c>
       <c r="E28">
-        <v>-26.3819406658535</v>
+        <v>-27.64802048586599</v>
       </c>
       <c r="F28">
-        <v>3.668084437047552</v>
+        <v>3.24705676416587</v>
       </c>
       <c r="G28">
-        <v>-5.600192816901338</v>
+        <v>-5.055118114951416</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.6226943640822458</v>
       </c>
       <c r="E29">
-        <v>-25.83087066386009</v>
+        <v>-28.03492877660733</v>
       </c>
       <c r="F29">
-        <v>3.608634165283438</v>
+        <v>3.276115892656077</v>
       </c>
       <c r="G29">
-        <v>-5.73736527132104</v>
+        <v>-4.794670876285872</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.7032306144328528</v>
       </c>
       <c r="E30">
-        <v>-25.81656521446986</v>
+        <v>-28.02844853030236</v>
       </c>
       <c r="F30">
-        <v>3.405316356470716</v>
+        <v>3.503626999834961</v>
       </c>
       <c r="G30">
-        <v>-5.690597194487755</v>
+        <v>-4.993671079197003</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.7042247432958629</v>
       </c>
       <c r="E31">
-        <v>-25.79255071680718</v>
+        <v>-26.17882954966146</v>
       </c>
       <c r="F31">
-        <v>3.428500703340268</v>
+        <v>3.341359766035371</v>
       </c>
       <c r="G31">
-        <v>-6.019476719995573</v>
+        <v>-5.383716244088395</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.6089026404233142</v>
       </c>
       <c r="E32">
-        <v>-25.61336352879767</v>
+        <v>-26.65763869191447</v>
       </c>
       <c r="F32">
-        <v>3.034737915154329</v>
+        <v>3.140802077408777</v>
       </c>
       <c r="G32">
-        <v>-5.465350986541283</v>
+        <v>-5.284048960083097</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.4097554818663661</v>
       </c>
       <c r="E33">
-        <v>-25.78925851620361</v>
+        <v>-25.91020047152646</v>
       </c>
       <c r="F33">
-        <v>2.970567605929062</v>
+        <v>3.180823820107633</v>
       </c>
       <c r="G33">
-        <v>-5.693017203276963</v>
+        <v>-5.314429836496989</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.1038990550991635</v>
       </c>
       <c r="E34">
-        <v>-24.63819287903792</v>
+        <v>-26.67765907550238</v>
       </c>
       <c r="F34">
-        <v>3.389844110121226</v>
+        <v>2.941816630112697</v>
       </c>
       <c r="G34">
-        <v>-6.228974662811733</v>
+        <v>-5.944208156614703</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.3064648807978838</v>
       </c>
       <c r="E35">
-        <v>-24.11278121077198</v>
+        <v>-25.14670881078125</v>
       </c>
       <c r="F35">
-        <v>3.651334848162946</v>
+        <v>3.266669190794551</v>
       </c>
       <c r="G35">
-        <v>-7.5402354032795</v>
+        <v>-5.397971453180497</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.8045482996028364</v>
       </c>
       <c r="E36">
-        <v>-24.34737427826533</v>
+        <v>-25.04095535728013</v>
       </c>
       <c r="F36">
-        <v>3.402344174229471</v>
+        <v>3.362184922541751</v>
       </c>
       <c r="G36">
-        <v>-6.955917494507057</v>
+        <v>-6.095222001934098</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.374829938975627</v>
       </c>
       <c r="E37">
-        <v>-24.17367560075312</v>
+        <v>-24.51674373462621</v>
       </c>
       <c r="F37">
-        <v>3.661817009277971</v>
+        <v>3.581786777758706</v>
       </c>
       <c r="G37">
-        <v>-7.136123730391744</v>
+        <v>-6.058594126087601</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.990843524341465</v>
       </c>
       <c r="E38">
-        <v>-22.93063212801765</v>
+        <v>-23.58747369740821</v>
       </c>
       <c r="F38">
-        <v>3.93819682301761</v>
+        <v>3.34619743166772</v>
       </c>
       <c r="G38">
-        <v>-6.962015519390394</v>
+        <v>-5.566604021859892</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.622566058868201</v>
       </c>
       <c r="E39">
-        <v>-23.19770341109401</v>
+        <v>-24.06890935458567</v>
       </c>
       <c r="F39">
-        <v>3.513310614773687</v>
+        <v>3.474861113405345</v>
       </c>
       <c r="G39">
-        <v>-6.450900393582316</v>
+        <v>-5.383080619344855</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.243911881778314</v>
       </c>
       <c r="E40">
-        <v>-21.43959130472611</v>
+        <v>-23.1667014780375</v>
       </c>
       <c r="F40">
-        <v>3.882003691881302</v>
+        <v>3.441173067868295</v>
       </c>
       <c r="G40">
-        <v>-7.27095893966072</v>
+        <v>-6.606257674649234</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.822756909351398</v>
       </c>
       <c r="E41">
-        <v>-21.84447763727791</v>
+        <v>-22.99195672302952</v>
       </c>
       <c r="F41">
-        <v>3.701444449093094</v>
+        <v>3.239058048524438</v>
       </c>
       <c r="G41">
-        <v>-6.64779508953047</v>
+        <v>-5.823469250251944</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.340250256992634</v>
       </c>
       <c r="E42">
-        <v>-20.18183934841372</v>
+        <v>-21.75365003410607</v>
       </c>
       <c r="F42">
-        <v>3.333717248377143</v>
+        <v>3.366489119566697</v>
       </c>
       <c r="G42">
-        <v>-7.142870622200779</v>
+        <v>-6.737302309275744</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.779252755650913</v>
       </c>
       <c r="E43">
-        <v>-20.70553019655675</v>
+        <v>-20.79630345804051</v>
       </c>
       <c r="F43">
-        <v>4.091181371701428</v>
+        <v>3.624562013704466</v>
       </c>
       <c r="G43">
-        <v>-7.531154576865279</v>
+        <v>-5.636075820001499</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.128683196192429</v>
       </c>
       <c r="E44">
-        <v>-19.68693600953745</v>
+        <v>-21.1824736075186</v>
       </c>
       <c r="F44">
-        <v>3.544901234046849</v>
+        <v>3.4858253843488</v>
       </c>
       <c r="G44">
-        <v>-7.438515581039853</v>
+        <v>-6.512575856978938</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.390560860186231</v>
       </c>
       <c r="E45">
-        <v>-19.34156288239446</v>
+        <v>-20.12653309535805</v>
       </c>
       <c r="F45">
-        <v>3.824198557779147</v>
+        <v>3.389231118243154</v>
       </c>
       <c r="G45">
-        <v>-7.128499544014803</v>
+        <v>-6.089349094147431</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.565233487098553</v>
       </c>
       <c r="E46">
-        <v>-20.38746829615402</v>
+        <v>-19.85061317407069</v>
       </c>
       <c r="F46">
-        <v>3.73354534268638</v>
+        <v>3.255627053315234</v>
       </c>
       <c r="G46">
-        <v>-6.779581286357777</v>
+        <v>-5.428120591406639</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.66908186249473</v>
       </c>
       <c r="E47">
-        <v>-19.54906661837393</v>
+        <v>-20.3543334518399</v>
       </c>
       <c r="F47">
-        <v>3.445243665285652</v>
+        <v>3.347787897081095</v>
       </c>
       <c r="G47">
-        <v>-6.748392636832303</v>
+        <v>-6.01531205370717</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.717993241240184</v>
       </c>
       <c r="E48">
-        <v>-18.13670350249166</v>
+        <v>-18.91784715491876</v>
       </c>
       <c r="F48">
-        <v>3.378273474238923</v>
+        <v>3.373336404518238</v>
       </c>
       <c r="G48">
-        <v>-6.865900450748733</v>
+        <v>-5.840419243413012</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.730990070388891</v>
       </c>
       <c r="E49">
-        <v>-17.39418320487598</v>
+        <v>-18.7240420528125</v>
       </c>
       <c r="F49">
-        <v>3.453297053175668</v>
+        <v>3.434733339678932</v>
       </c>
       <c r="G49">
-        <v>-6.97447972334575</v>
+        <v>-6.003513269405207</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.733282505301905</v>
       </c>
       <c r="E50">
-        <v>-17.47508439302301</v>
+        <v>-18.42679754742302</v>
       </c>
       <c r="F50">
-        <v>3.685195194119779</v>
+        <v>3.307022280454526</v>
       </c>
       <c r="G50">
-        <v>-8.189327446073323</v>
+        <v>-5.738166423341543</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.73668274033698</v>
       </c>
       <c r="E51">
-        <v>-16.39201379308249</v>
+        <v>-17.38697387425576</v>
       </c>
       <c r="F51">
-        <v>3.29622036952202</v>
+        <v>3.456161547654549</v>
       </c>
       <c r="G51">
-        <v>-7.403711815785496</v>
+        <v>-6.03538720185731</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.762490672985273</v>
       </c>
       <c r="E52">
-        <v>-16.2884657064231</v>
+        <v>-17.59099521372334</v>
       </c>
       <c r="F52">
-        <v>3.315441806736581</v>
+        <v>3.194776840640388</v>
       </c>
       <c r="G52">
-        <v>-7.646013954350293</v>
+        <v>-6.211888937283554</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.818180615517594</v>
       </c>
       <c r="E53">
-        <v>-15.7127200495619</v>
+        <v>-16.88650956929807</v>
       </c>
       <c r="F53">
-        <v>3.28269478656911</v>
+        <v>3.261539939836417</v>
       </c>
       <c r="G53">
-        <v>-6.851880290389921</v>
+        <v>-4.997411995656379</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.908137594173346</v>
       </c>
       <c r="E54">
-        <v>-15.19793670979196</v>
+        <v>-16.53388182679479</v>
       </c>
       <c r="F54">
-        <v>3.366015293412296</v>
+        <v>3.391099915103871</v>
       </c>
       <c r="G54">
-        <v>-6.852873454051702</v>
+        <v>-6.012868871099188</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.039149307846545</v>
       </c>
       <c r="E55">
-        <v>-15.96614704045316</v>
+        <v>-16.84621973605183</v>
       </c>
       <c r="F55">
-        <v>3.199026365416749</v>
+        <v>3.264083027763011</v>
       </c>
       <c r="G55">
-        <v>-7.20082503241126</v>
+        <v>-6.40740975683291</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.200292387879205</v>
       </c>
       <c r="E56">
-        <v>-15.0794718297513</v>
+        <v>-16.07975286788358</v>
       </c>
       <c r="F56">
-        <v>3.122912654977919</v>
+        <v>3.133818940203177</v>
       </c>
       <c r="G56">
-        <v>-8.006039092291573</v>
+        <v>-6.42058241753367</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.394297569364972</v>
       </c>
       <c r="E57">
-        <v>-14.52194422382296</v>
+        <v>-14.64029136353941</v>
       </c>
       <c r="F57">
-        <v>3.089135145761367</v>
+        <v>3.032613981133551</v>
       </c>
       <c r="G57">
-        <v>-7.562521995849873</v>
+        <v>-6.311486699832527</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.611074810417116</v>
       </c>
       <c r="E58">
-        <v>-14.72446663839399</v>
+        <v>-13.98574573047074</v>
       </c>
       <c r="F58">
-        <v>3.225285612085493</v>
+        <v>2.630883955267486</v>
       </c>
       <c r="G58">
-        <v>-7.74314204992697</v>
+        <v>-6.573529621447999</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.840433981555273</v>
       </c>
       <c r="E59">
-        <v>-14.13485932259531</v>
+        <v>-14.1491421296155</v>
       </c>
       <c r="F59">
-        <v>3.110472233322676</v>
+        <v>3.32093056914753</v>
       </c>
       <c r="G59">
-        <v>-7.954599835702377</v>
+        <v>-6.915922793847121</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.080227763944398</v>
       </c>
       <c r="E60">
-        <v>-13.70423767225792</v>
+        <v>-14.37429785727687</v>
       </c>
       <c r="F60">
-        <v>3.555267423725482</v>
+        <v>3.36735393513522</v>
       </c>
       <c r="G60">
-        <v>-7.924943968761586</v>
+        <v>-6.667261097301384</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.313010242402885</v>
       </c>
       <c r="E61">
-        <v>-14.93749511266282</v>
+        <v>-14.12545821055539</v>
       </c>
       <c r="F61">
-        <v>3.10439864352535</v>
+        <v>3.068281824763292</v>
       </c>
       <c r="G61">
-        <v>-7.918369225320594</v>
+        <v>-7.239740495225393</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.538624509533493</v>
       </c>
       <c r="E62">
-        <v>-14.53416204669565</v>
+        <v>-13.57888951172561</v>
       </c>
       <c r="F62">
-        <v>2.623151973929755</v>
+        <v>3.138467738067688</v>
       </c>
       <c r="G62">
-        <v>-8.301826404588835</v>
+        <v>-7.110265059184497</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.747430644631634</v>
       </c>
       <c r="E63">
-        <v>-12.94618018032192</v>
+        <v>-14.89803399015998</v>
       </c>
       <c r="F63">
-        <v>2.921874513257702</v>
+        <v>3.341707680344547</v>
       </c>
       <c r="G63">
-        <v>-8.457600814393702</v>
+        <v>-7.614901447372222</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.930037890547903</v>
       </c>
       <c r="E64">
-        <v>-13.18677800434945</v>
+        <v>-12.93779797493372</v>
       </c>
       <c r="F64">
-        <v>3.04675752616895</v>
+        <v>2.518383378293285</v>
       </c>
       <c r="G64">
-        <v>-8.536431524774828</v>
+        <v>-8.245216075867299</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.086901505797634</v>
       </c>
       <c r="E65">
-        <v>-12.8508784448305</v>
+        <v>-13.03672701810529</v>
       </c>
       <c r="F65">
-        <v>2.720816490719817</v>
+        <v>3.020546324809568</v>
       </c>
       <c r="G65">
-        <v>-8.523891178272068</v>
+        <v>-7.331108241563739</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.203961466824996</v>
       </c>
       <c r="E66">
-        <v>-12.78838550352465</v>
+        <v>-12.80309851557557</v>
       </c>
       <c r="F66">
-        <v>2.763136124594038</v>
+        <v>2.634500607348108</v>
       </c>
       <c r="G66">
-        <v>-8.412600568878389</v>
+        <v>-7.816960594361639</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.283360217337414</v>
       </c>
       <c r="E67">
-        <v>-13.38079594473407</v>
+        <v>-13.51664563649018</v>
       </c>
       <c r="F67">
-        <v>2.865109808613463</v>
+        <v>2.707638822076082</v>
       </c>
       <c r="G67">
-        <v>-8.613183212557292</v>
+        <v>-7.757082757192841</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.319199211892338</v>
       </c>
       <c r="E68">
-        <v>-12.51158252980579</v>
+        <v>-13.46733055454665</v>
       </c>
       <c r="F68">
-        <v>2.88342501188936</v>
+        <v>2.711404580289209</v>
       </c>
       <c r="G68">
-        <v>-8.486170822397613</v>
+        <v>-7.369788655644584</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.306022516563067</v>
       </c>
       <c r="E69">
-        <v>-13.06262083248115</v>
+        <v>-12.84577032614984</v>
       </c>
       <c r="F69">
-        <v>2.848842329557286</v>
+        <v>2.472660811128363</v>
       </c>
       <c r="G69">
-        <v>-7.567275939244267</v>
+        <v>-8.347710565763135</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.248767088124618</v>
       </c>
       <c r="E70">
-        <v>-13.47767358918017</v>
+        <v>-12.7867054396678</v>
       </c>
       <c r="F70">
-        <v>2.896758413604821</v>
+        <v>2.593039162103187</v>
       </c>
       <c r="G70">
-        <v>-8.258243072564332</v>
+        <v>-7.861460947500523</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.13986032172286</v>
       </c>
       <c r="E71">
-        <v>-12.94378914604587</v>
+        <v>-13.40609200054092</v>
       </c>
       <c r="F71">
-        <v>2.987588899321787</v>
+        <v>2.171131763039732</v>
       </c>
       <c r="G71">
-        <v>-7.829239407766796</v>
+        <v>-7.353802031235443</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.987734370571097</v>
       </c>
       <c r="E72">
-        <v>-12.42813181079245</v>
+        <v>-13.7120764607652</v>
       </c>
       <c r="F72">
-        <v>2.764501274073852</v>
+        <v>2.529952357440783</v>
       </c>
       <c r="G72">
-        <v>-7.658875423770361</v>
+        <v>-7.525798114182738</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.793187689879414</v>
       </c>
       <c r="E73">
-        <v>-13.7982759635012</v>
+        <v>-13.53558824326426</v>
       </c>
       <c r="F73">
-        <v>2.659167731868672</v>
+        <v>2.069686577423294</v>
       </c>
       <c r="G73">
-        <v>-7.593813272287065</v>
+        <v>-7.904160363866042</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.557553836433847</v>
       </c>
       <c r="E74">
-        <v>-14.22811871630928</v>
+        <v>-14.06322792074198</v>
       </c>
       <c r="F74">
-        <v>2.985668743682097</v>
+        <v>2.069391678627897</v>
       </c>
       <c r="G74">
-        <v>-7.686905812851371</v>
+        <v>-7.885790146668626</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.291074838273561</v>
       </c>
       <c r="E75">
-        <v>-14.17576049983259</v>
+        <v>-13.01376312641239</v>
       </c>
       <c r="F75">
-        <v>2.686316645128023</v>
+        <v>2.071328401615642</v>
       </c>
       <c r="G75">
-        <v>-6.957983274923562</v>
+        <v>-7.06437427691912</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.991312778159313</v>
       </c>
       <c r="E76">
-        <v>-14.04976929599118</v>
+        <v>-13.53916120925631</v>
       </c>
       <c r="F76">
-        <v>2.370281227081567</v>
+        <v>2.011782039232803</v>
       </c>
       <c r="G76">
-        <v>-6.879910679470929</v>
+        <v>-7.312953209826375</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.67006562130921</v>
       </c>
       <c r="E77">
-        <v>-14.32141886628931</v>
+        <v>-14.39605264640972</v>
       </c>
       <c r="F77">
-        <v>2.693723906443856</v>
+        <v>2.166259305976465</v>
       </c>
       <c r="G77">
-        <v>-6.746800264427914</v>
+        <v>-7.286531745877452</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.330309823632406</v>
       </c>
       <c r="E78">
-        <v>-15.01180737112869</v>
+        <v>-14.77618181156159</v>
       </c>
       <c r="F78">
-        <v>2.412947118530158</v>
+        <v>1.806544074780391</v>
       </c>
       <c r="G78">
-        <v>-6.416371403607717</v>
+        <v>-6.603940292771744</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.974494989817656</v>
       </c>
       <c r="E79">
-        <v>-16.24380589575946</v>
+        <v>-15.47541442613795</v>
       </c>
       <c r="F79">
-        <v>2.149433507290802</v>
+        <v>1.617517260400766</v>
       </c>
       <c r="G79">
-        <v>-5.959615435554471</v>
+        <v>-6.407171397554082</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.611545304627016</v>
       </c>
       <c r="E80">
-        <v>-16.84774130331841</v>
+        <v>-16.10908832250527</v>
       </c>
       <c r="F80">
-        <v>2.489806359631507</v>
+        <v>1.944169035081501</v>
       </c>
       <c r="G80">
-        <v>-6.358049522842377</v>
+        <v>-6.001781854088168</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.237697034705636</v>
       </c>
       <c r="E81">
-        <v>-16.44813064298554</v>
+        <v>-16.92353890125879</v>
       </c>
       <c r="F81">
-        <v>2.11860332929341</v>
+        <v>1.915490955596582</v>
       </c>
       <c r="G81">
-        <v>-5.953772322677658</v>
+        <v>-4.603202164476584</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.861112546688112</v>
       </c>
       <c r="E82">
-        <v>-17.21859615370256</v>
+        <v>-17.72170961595474</v>
       </c>
       <c r="F82">
-        <v>2.214510050454731</v>
+        <v>1.775525029015161</v>
       </c>
       <c r="G82">
-        <v>-5.401672643093402</v>
+        <v>-4.92727146731584</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.482463665616198</v>
       </c>
       <c r="E83">
-        <v>-18.3629053076488</v>
+        <v>-18.33712923359714</v>
       </c>
       <c r="F83">
-        <v>2.58803913645989</v>
+        <v>1.742539439035685</v>
       </c>
       <c r="G83">
-        <v>-4.767130447944676</v>
+        <v>-5.331853237670172</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.103196601610491</v>
       </c>
       <c r="E84">
-        <v>-19.57256034152572</v>
+        <v>-19.24660078245361</v>
       </c>
       <c r="F84">
-        <v>2.206025911515258</v>
+        <v>1.707665171377825</v>
       </c>
       <c r="G84">
-        <v>-4.379799930395486</v>
+        <v>-4.84814611838172</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.734066282414915</v>
       </c>
       <c r="E85">
-        <v>-20.56914161639374</v>
+        <v>-20.27700975815893</v>
       </c>
       <c r="F85">
-        <v>2.024505762539803</v>
+        <v>1.606799842943347</v>
       </c>
       <c r="G85">
-        <v>-3.558996511570745</v>
+        <v>-4.585811868758793</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.376597338132198</v>
       </c>
       <c r="E86">
-        <v>-21.42328426982449</v>
+        <v>-22.16140289070472</v>
       </c>
       <c r="F86">
-        <v>2.263345622319373</v>
+        <v>1.575630034310807</v>
       </c>
       <c r="G86">
-        <v>-3.842442110097605</v>
+        <v>-4.171384535970668</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.044227973037823</v>
       </c>
       <c r="E87">
-        <v>-22.94653612873259</v>
+        <v>-22.39079727003727</v>
       </c>
       <c r="F87">
-        <v>1.83576059307713</v>
+        <v>1.77473476651289</v>
       </c>
       <c r="G87">
-        <v>-3.959443410546527</v>
+        <v>-3.767004708894232</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.747125849431131</v>
       </c>
       <c r="E88">
-        <v>-24.26718406053751</v>
+        <v>-24.05272911695626</v>
       </c>
       <c r="F88">
-        <v>1.844870977773119</v>
+        <v>1.421894984760052</v>
       </c>
       <c r="G88">
-        <v>-3.819639072423105</v>
+        <v>-3.640796781300597</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.492410873709095</v>
       </c>
       <c r="E89">
-        <v>-25.15840585914306</v>
+        <v>-26.23390032206874</v>
       </c>
       <c r="F89">
-        <v>1.91948202974327</v>
+        <v>1.229987108553491</v>
       </c>
       <c r="G89">
-        <v>-3.392207916756723</v>
+        <v>-3.644815783585272</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.297733885512866</v>
       </c>
       <c r="E90">
-        <v>-27.45860347507315</v>
+        <v>-26.58506083899354</v>
       </c>
       <c r="F90">
-        <v>1.634127683561702</v>
+        <v>1.31706674667058</v>
       </c>
       <c r="G90">
-        <v>-2.81583862782407</v>
+        <v>-2.807237830513044</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.169580138614877</v>
       </c>
       <c r="E91">
-        <v>-28.50192313017433</v>
+        <v>-28.49560138045963</v>
       </c>
       <c r="F91">
-        <v>1.40157513236938</v>
+        <v>1.00139415354655</v>
       </c>
       <c r="G91">
-        <v>-3.260425030474955</v>
+        <v>-3.503472041786089</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.1203078574226</v>
       </c>
       <c r="E92">
-        <v>-29.91927209593905</v>
+        <v>-31.73085642338952</v>
       </c>
       <c r="F92">
-        <v>1.161827381916342</v>
+        <v>1.295222698258757</v>
       </c>
       <c r="G92">
-        <v>-3.011339584100191</v>
+        <v>-3.088180656612215</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.16011027302751</v>
       </c>
       <c r="E93">
-        <v>-32.35316611423459</v>
+        <v>-32.70275751491573</v>
       </c>
       <c r="F93">
-        <v>1.441623382825125</v>
+        <v>0.8306709452991833</v>
       </c>
       <c r="G93">
-        <v>-3.100293942740408</v>
+        <v>-3.394412740085878</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.287061950798495</v>
       </c>
       <c r="E94">
-        <v>-34.30424781925435</v>
+        <v>-34.9793844236359</v>
       </c>
       <c r="F94">
-        <v>1.382958403358864</v>
+        <v>0.5548784440481299</v>
       </c>
       <c r="G94">
-        <v>-3.430497686463934</v>
+        <v>-3.322765913524971</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.505889949986987</v>
       </c>
       <c r="E95">
-        <v>-36.23087350039567</v>
+        <v>-36.76754521928169</v>
       </c>
       <c r="F95">
-        <v>0.9571063187232774</v>
+        <v>0.5883486289582439</v>
       </c>
       <c r="G95">
-        <v>-2.887515249294831</v>
+        <v>-2.91740616496891</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.812114582152345</v>
       </c>
       <c r="E96">
-        <v>-38.96493968252665</v>
+        <v>-39.03869267445258</v>
       </c>
       <c r="F96">
-        <v>0.7547113111972742</v>
+        <v>0.6918398820595973</v>
       </c>
       <c r="G96">
-        <v>-3.321845581865054</v>
+        <v>-3.925834752231846</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.189322748934909</v>
       </c>
       <c r="E97">
-        <v>-40.39193656216471</v>
+        <v>-41.14900005405603</v>
       </c>
       <c r="F97">
-        <v>0.7864957684426912</v>
+        <v>0.2116286717175015</v>
       </c>
       <c r="G97">
-        <v>-3.549700499696471</v>
+        <v>-3.147052087937074</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.640452155645115</v>
       </c>
       <c r="E98">
-        <v>-43.93942535944947</v>
+        <v>-43.12272639335114</v>
       </c>
       <c r="F98">
-        <v>0.481644967068834</v>
+        <v>0.1863568389928942</v>
       </c>
       <c r="G98">
-        <v>-3.348518647274962</v>
+        <v>-4.322441418382073</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.125084001227989</v>
       </c>
       <c r="E99">
-        <v>-45.19949815869079</v>
+        <v>-45.96686166471255</v>
       </c>
       <c r="F99">
-        <v>0.119735390622744</v>
+        <v>0.01827032418863814</v>
       </c>
       <c r="G99">
-        <v>-3.948548405176786</v>
+        <v>-4.25909081894258</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.663448358924994</v>
       </c>
       <c r="E100">
-        <v>-48.10738302289518</v>
+        <v>-48.59833526819976</v>
       </c>
       <c r="F100">
-        <v>-0.2104361171524858</v>
+        <v>-0.212129300123808</v>
       </c>
       <c r="G100">
-        <v>-3.936862179423158</v>
+        <v>-4.827915374591234</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.18870791210136</v>
       </c>
       <c r="E101">
-        <v>-49.77104701112211</v>
+        <v>-49.72432108419246</v>
       </c>
       <c r="F101">
-        <v>-0.342713137501122</v>
+        <v>-0.2991758035447856</v>
       </c>
       <c r="G101">
-        <v>-4.167550924236193</v>
+        <v>-4.594988700993652</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.768493434174313</v>
       </c>
       <c r="E102">
-        <v>-51.42505289640917</v>
+        <v>-52.33237908070451</v>
       </c>
       <c r="F102">
-        <v>-0.7814397083110186</v>
+        <v>-0.4296676921403889</v>
       </c>
       <c r="G102">
-        <v>-4.907808770090465</v>
+        <v>-4.740387861078443</v>
       </c>
     </row>
   </sheetData>
